--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20211.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="47">
   <si>
     <t>Mat</t>
   </si>
@@ -85,37 +85,79 @@
     <t>CABRERA</t>
   </si>
   <si>
-    <t>APALE</t>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>VALDES</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>COLOHUA</t>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>CALPULALPAN</t>
   </si>
   <si>
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>CALPULALPAN</t>
-  </si>
-  <si>
     <t>AYELEN</t>
   </si>
   <si>
-    <t>EVELYN AISHA</t>
+    <t>ASTRID</t>
+  </si>
+  <si>
+    <t>BRENDA ELENA</t>
+  </si>
+  <si>
+    <t>ELEAZAR RIGOBERTO</t>
+  </si>
+  <si>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>YARELY JACQUELINE</t>
+  </si>
+  <si>
+    <t>DANIELA JAQUELINE</t>
   </si>
   <si>
     <t>JOSE JAZAEL</t>
-  </si>
-  <si>
-    <t>YARELY JACQUELINE</t>
   </si>
 </sst>
 </file>
@@ -1040,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1078,10 +1120,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1090,21 +1132,21 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920358</v>
+        <v>19330051920436</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1113,53 +1155,168 @@
         <v>14</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920085</v>
+        <v>18330051920188</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920429</v>
+        <v>19330051920092</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>19330051920095</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920207</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920429</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920244</v>
+      </c>
+      <c r="B9" t="s">
         <v>28</v>
       </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="G5">
-        <v>6</v>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>19330051920085</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20211.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20211.xlsx
@@ -97,18 +97,18 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -124,15 +124,15 @@
     <t>MORALES</t>
   </si>
   <si>
+    <t>CALPULALPAN</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>CALPULALPAN</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
     <t>AYELEN</t>
   </si>
   <si>
@@ -148,16 +148,16 @@
     <t>JAFET</t>
   </si>
   <si>
+    <t>YARELY JACQUELINE</t>
+  </si>
+  <si>
+    <t>DANIELA JAQUELINE</t>
+  </si>
+  <si>
+    <t>JOSE JAZAEL</t>
+  </si>
+  <si>
     <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>YARELY JACQUELINE</t>
-  </si>
-  <si>
-    <t>DANIELA JAQUELINE</t>
-  </si>
-  <si>
-    <t>JOSE JAZAEL</t>
   </si>
 </sst>
 </file>
@@ -1132,7 +1132,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1229,7 +1229,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920207</v>
+        <v>19330051920429</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1244,21 +1244,21 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920429</v>
+        <v>19330051920244</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
         <v>44</v>
@@ -1270,18 +1270,18 @@
         <v>10</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920244</v>
+        <v>19330051920085</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
         <v>45</v>
@@ -1290,15 +1290,15 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920085</v>
+        <v>19330051920207</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
@@ -1313,10 +1313,10 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20211.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="76">
   <si>
     <t>Mat</t>
   </si>
@@ -85,9 +85,21 @@
     <t>CABRERA</t>
   </si>
   <si>
+    <t>HERAS</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
     <t>VALDES</t>
   </si>
   <si>
@@ -97,13 +109,28 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>ANTONIO</t>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LIMA</t>
   </si>
   <si>
     <t>MIXCOHUA</t>
@@ -112,9 +139,18 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>MARIN</t>
   </si>
   <si>
@@ -124,10 +160,28 @@
     <t>MORALES</t>
   </si>
   <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>CALPULALPAN</t>
   </si>
   <si>
-    <t>TEXOCO</t>
+    <t>LLAVE</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>MORO</t>
+  </si>
+  <si>
+    <t>MARINERO</t>
   </si>
   <si>
     <t>ZEPAHUA</t>
@@ -136,9 +190,21 @@
     <t>AYELEN</t>
   </si>
   <si>
+    <t>CESAR ENRIQUE</t>
+  </si>
+  <si>
+    <t>MARLENE ALICIA</t>
+  </si>
+  <si>
     <t>ASTRID</t>
   </si>
   <si>
+    <t>ITZEL ISABEL</t>
+  </si>
+  <si>
+    <t>JENNIFER</t>
+  </si>
+  <si>
     <t>BRENDA ELENA</t>
   </si>
   <si>
@@ -148,13 +214,34 @@
     <t>JAFET</t>
   </si>
   <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
     <t>YARELY JACQUELINE</t>
   </si>
   <si>
     <t>DANIELA JAQUELINE</t>
   </si>
   <si>
-    <t>JOSE JAZAEL</t>
+    <t>YESUA ISIDRO</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>DENISSE</t>
+  </si>
+  <si>
+    <t>GUILLERMO UBALDO</t>
   </si>
   <si>
     <t>ALEXIS</t>
@@ -584,10 +671,10 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>18</v>
@@ -636,10 +723,10 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>20</v>
@@ -648,7 +735,7 @@
         <v>62.5</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -688,10 +775,10 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7">
         <v>27</v>
@@ -700,7 +787,7 @@
         <v>75</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -753,16 +840,19 @@
         <v>35</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H2">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -776,16 +866,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>53.85</v>
+      </c>
+      <c r="H3">
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -799,16 +892,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>82.61</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -822,16 +918,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>53.13</v>
+      </c>
+      <c r="H5">
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -845,16 +944,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>88.23999999999999</v>
+      </c>
+      <c r="H6">
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -868,16 +970,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>63.89</v>
+      </c>
+      <c r="H7">
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -956,19 +1061,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>69.23</v>
+        <v>53.85</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -985,16 +1090,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>82.61</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1008,19 +1113,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>62.5</v>
+        <v>56.25</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1037,13 +1142,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>94.12</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H6">
         <v>7.6</v>
@@ -1060,19 +1165,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G7">
-        <v>75</v>
+        <v>69.44</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -1082,7 +1187,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1120,10 +1225,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1137,45 +1242,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920436</v>
+        <v>19330051920235</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>18330051920188</v>
+        <v>19330051920140</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1183,22 +1288,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920092</v>
+        <v>19330051920436</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1206,85 +1311,85 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920095</v>
+        <v>19330051920393</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920429</v>
+        <v>19330051920369</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920244</v>
+        <v>18330051920188</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920085</v>
+        <v>19330051920092</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1293,29 +1398,282 @@
         <v>12</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920207</v>
+        <v>19330051920095</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920116</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>19330051920119</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920430</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920429</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>19330051920244</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>19330051920245</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>19330051920139</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>19330051920431</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>19330051920201</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>19330051920203</v>
+      </c>
+      <c r="B20" t="s">
         <v>37</v>
       </c>
-      <c r="D10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
         <v>13</v>
       </c>
-      <c r="G10">
+      <c r="G20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>19330051920207</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20211.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="88">
   <si>
     <t>Mat</t>
   </si>
@@ -82,100 +82,121 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>VALDES</t>
+  </si>
+  <si>
+    <t>CITLAHUA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
     <t>CABRERA</t>
   </si>
   <si>
+    <t>MIXCOAC</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>HERAS</t>
   </si>
   <si>
-    <t>SOLIS</t>
+    <t>LADINO</t>
+  </si>
+  <si>
+    <t>LICEA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LIMA</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>VALDES</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LIMA</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>CALPULALPAN</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>LLAVE</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>CALPULALPAN</t>
-  </si>
-  <si>
-    <t>LLAVE</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
+    <t>GARATE</t>
+  </si>
+  <si>
+    <t>LUNA</t>
   </si>
   <si>
     <t>MORO</t>
@@ -187,55 +208,70 @@
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>FRANCISCO EMMANUEL</t>
+  </si>
+  <si>
+    <t>KAROL</t>
+  </si>
+  <si>
+    <t>EVELYN AISHA</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>BRENDA ELENA</t>
+  </si>
+  <si>
+    <t>RAUL ARTURO</t>
+  </si>
+  <si>
+    <t>JUAN ANTONIO</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
     <t>AYELEN</t>
   </si>
   <si>
+    <t>ELYDEN JULYSSA</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>YARELY JACQUELINE</t>
+  </si>
+  <si>
     <t>CESAR ENRIQUE</t>
   </si>
   <si>
-    <t>MARLENE ALICIA</t>
-  </si>
-  <si>
-    <t>ASTRID</t>
-  </si>
-  <si>
-    <t>ITZEL ISABEL</t>
+    <t>ZURISADAI</t>
+  </si>
+  <si>
+    <t>QADMIEL TAMARA</t>
+  </si>
+  <si>
+    <t>DANIELA JAQUELINE</t>
+  </si>
+  <si>
+    <t>YESUA ISIDRO</t>
+  </si>
+  <si>
+    <t>ZURI SADAY</t>
   </si>
   <si>
     <t>JENNIFER</t>
   </si>
   <si>
-    <t>BRENDA ELENA</t>
-  </si>
-  <si>
-    <t>ELEAZAR RIGOBERTO</t>
-  </si>
-  <si>
-    <t>JAFET</t>
-  </si>
-  <si>
     <t>JOSUE</t>
   </si>
   <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>YARELY JACQUELINE</t>
-  </si>
-  <si>
-    <t>DANIELA JAQUELINE</t>
-  </si>
-  <si>
-    <t>YESUA ISIDRO</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
+    <t>ARIAN ALEXIS</t>
   </si>
   <si>
     <t>DENISSE</t>
@@ -840,7 +876,7 @@
         <v>35</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -852,7 +888,7 @@
         <v>85.70999999999999</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -918,19 +954,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>53.13</v>
+        <v>56.25</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1047,7 +1083,7 @@
         <v>85.70999999999999</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1090,13 +1126,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>82.61</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H4">
         <v>7.7</v>
@@ -1116,16 +1152,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>56.25</v>
+        <v>84.38</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1187,7 +1223,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1219,16 +1255,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920151</v>
+        <v>19330051920155</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1237,27 +1273,27 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920235</v>
+        <v>19330051920181</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1265,22 +1301,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920140</v>
+        <v>19330051920358</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1288,16 +1324,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920436</v>
+        <v>19330051920366</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1311,16 +1347,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920393</v>
+        <v>18330051920188</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1329,27 +1365,27 @@
         <v>14</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920369</v>
+        <v>19330051920091</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1357,22 +1393,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>18330051920188</v>
+        <v>19330051920098</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1380,16 +1416,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920092</v>
+        <v>19330051920109</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1403,85 +1439,85 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920095</v>
+        <v>19330051920151</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920116</v>
+        <v>19330051920168</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920119</v>
+        <v>19330051920430</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920430</v>
+        <v>19330051920233</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1498,13 +1534,13 @@
         <v>19330051920429</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1518,16 +1554,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920244</v>
+        <v>19330051920235</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1541,16 +1577,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920245</v>
+        <v>19330051920236</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1564,22 +1600,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920139</v>
+        <v>19330051920237</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1587,45 +1623,45 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920431</v>
+        <v>19330051920244</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920201</v>
+        <v>19330051920245</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1633,47 +1669,162 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920203</v>
+        <v>19330051920367</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
         <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
+        <v>19330051920369</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>19330051920094</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>19330051920001</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>19330051920201</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>19330051920203</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
         <v>19330051920207</v>
       </c>
-      <c r="B21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
         <v>13</v>
       </c>
-      <c r="G21">
+      <c r="G26">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20211.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="63">
   <si>
     <t>Mat</t>
   </si>
@@ -91,9 +91,6 @@
     <t>APALE</t>
   </si>
   <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
     <t>VALDES</t>
   </si>
   <si>
@@ -112,100 +109,58 @@
     <t>MIXCOAC</t>
   </si>
   <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>LADINO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>GROTH</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>HERAS</t>
-  </si>
-  <si>
-    <t>LADINO</t>
-  </si>
-  <si>
-    <t>LICEA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LIMA</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>CALPULALPAN</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>LLAVE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>GARATE</t>
   </si>
   <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>MORO</t>
-  </si>
-  <si>
-    <t>MARINERO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
   </si>
   <si>
     <t>FRANCISCO EMMANUEL</t>
@@ -217,9 +172,6 @@
     <t>EVELYN AISHA</t>
   </si>
   <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
     <t>BRENDA ELENA</t>
   </si>
   <si>
@@ -238,49 +190,22 @@
     <t>ELYDEN JULYSSA</t>
   </si>
   <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
     <t>URIEL</t>
   </si>
   <si>
-    <t>YARELY JACQUELINE</t>
-  </si>
-  <si>
-    <t>CESAR ENRIQUE</t>
-  </si>
-  <si>
     <t>ZURISADAI</t>
   </si>
   <si>
-    <t>QADMIEL TAMARA</t>
-  </si>
-  <si>
-    <t>DANIELA JAQUELINE</t>
-  </si>
-  <si>
-    <t>YESUA ISIDRO</t>
-  </si>
-  <si>
-    <t>ZURI SADAY</t>
-  </si>
-  <si>
-    <t>JENNIFER</t>
-  </si>
-  <si>
     <t>JOSUE</t>
   </si>
   <si>
     <t>ARIAN ALEXIS</t>
   </si>
   <si>
-    <t>DENISSE</t>
-  </si>
-  <si>
-    <t>GUILLERMO UBALDO</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
+    <t>ARELY</t>
+  </si>
+  <si>
+    <t>DIANA</t>
   </si>
 </sst>
 </file>
@@ -902,7 +827,7 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>12</v>
@@ -914,7 +839,7 @@
         <v>53.85</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -980,7 +905,7 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -992,7 +917,7 @@
         <v>88.23999999999999</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1006,19 +931,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>63.89</v>
+        <v>72.22</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1100,16 +1025,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>53.85</v>
+        <v>76.92</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1178,16 +1103,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>88.23999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1204,13 +1129,13 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>69.44</v>
+        <v>86.11</v>
       </c>
       <c r="H7">
         <v>6.9</v>
@@ -1223,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1261,10 +1186,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1284,10 +1209,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1307,10 +1232,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1324,16 +1249,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920366</v>
+        <v>18330051920188</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1347,22 +1272,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>18330051920188</v>
+        <v>19330051920091</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1370,16 +1295,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920091</v>
+        <v>19330051920098</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1393,16 +1318,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920098</v>
+        <v>19330051920109</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1416,39 +1341,39 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920109</v>
+        <v>19330051920151</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920151</v>
+        <v>19330051920168</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1462,22 +1387,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920168</v>
+        <v>19330051920233</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1485,16 +1410,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920430</v>
+        <v>19330051920236</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1508,22 +1433,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920233</v>
+        <v>19330051920094</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1531,22 +1456,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920429</v>
+        <v>19330051920001</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1554,22 +1479,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920235</v>
+        <v>19330051920194</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1577,254 +1502,24 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920236</v>
+        <v>19330051920204</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330051920237</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" t="s">
-        <v>78</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330051920244</v>
-      </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" t="s">
-        <v>79</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>19330051920245</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" t="s">
-        <v>80</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920367</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>19330051920369</v>
-      </c>
-      <c r="B21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>19330051920094</v>
-      </c>
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" t="s">
-        <v>83</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>19330051920001</v>
-      </c>
-      <c r="B23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" t="s">
-        <v>84</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>19330051920201</v>
-      </c>
-      <c r="B24" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>19330051920203</v>
-      </c>
-      <c r="B25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" t="s">
-        <v>86</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>19330051920207</v>
-      </c>
-      <c r="B26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" t="s">
-        <v>87</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26">
         <v>1</v>
       </c>
     </row>
